--- a/बजेट माग estimate/नगर बजेट estimate/देबीस्थान खानीडाँडा सिँचाई/देबीस्थान खानीडाँडा सिँचाई.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/देबीस्थान खानीडाँडा सिँचाई/देबीस्थान खानीडाँडा सिँचाई.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79861A70-6D4D-4A5F-9226-CC3A51AB488C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
@@ -36,10 +37,10 @@
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -48,6 +49,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -55,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -194,14 +197,17 @@
   <si>
     <t>Earthwork Excavation in Cutting., Roadway Excavation in all types of Soil by Manual Means ., Roadway Excavation in all types of soil as per drawing and technical specification, including removal of stumps and other deleterious matter, with all lifts and lead as per Drawing and instruction of the Engineer.</t>
   </si>
+  <si>
+    <t>Provisional sum for unforseen works</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -361,13 +367,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -375,7 +381,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -399,14 +405,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -425,7 +431,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -440,7 +446,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -457,7 +463,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -477,32 +500,14 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3"/>
+    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="5"/>
-    <cellStyle name="Percent 2" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -518,7 +523,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -612,7 +617,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -671,7 +676,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -735,9 +740,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -775,9 +780,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -812,7 +817,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -847,7 +852,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1020,135 +1025,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S56"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="19" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="19" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="19"/>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="19"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.109375" style="19"/>
+    <col min="9" max="9" width="9.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.109375" style="19"/>
+    <col min="17" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-    </row>
-    <row r="2" spans="1:16" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+    </row>
+    <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="49" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-    </row>
-    <row r="5" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="50" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+    </row>
+    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-    </row>
-    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+    </row>
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="46" t="s">
+      <c r="H6" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-    </row>
-    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+    </row>
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>6</v>
       </c>
@@ -1183,7 +1188,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>1</v>
       </c>
@@ -1200,7 +1205,7 @@
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="32" t="s">
         <v>30</v>
@@ -1217,11 +1222,11 @@
         <v>1.5</v>
       </c>
       <c r="F10" s="33">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G10" s="33">
         <f>PRODUCT(C10:F10)</f>
-        <v>18.75</v>
+        <v>11.25</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
@@ -1241,7 +1246,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="32"/>
       <c r="C11" s="17">
@@ -1256,22 +1261,22 @@
         <v>1.25</v>
       </c>
       <c r="F11" s="33">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G11" s="33">
         <f>PRODUCT(C11:F11)</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="32"/>
       <c r="C12" s="17">
@@ -1296,12 +1301,12 @@
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-    </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+    </row>
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="34" t="s">
         <v>17</v>
@@ -1312,7 +1317,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="6">
         <f>SUM(G10:G12)</f>
-        <v>36</v>
+        <v>22.5</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>18</v>
@@ -1322,11 +1327,11 @@
       </c>
       <c r="J13" s="18">
         <f>G13*I13</f>
-        <v>26960.399999999998</v>
+        <v>16850.25</v>
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -1339,7 +1344,7 @@
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
     </row>
-    <row r="15" spans="1:16" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>2</v>
       </c>
@@ -1356,7 +1361,7 @@
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="32" t="str">
         <f>B10</f>
@@ -1398,7 +1403,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="32"/>
       <c r="C17" s="17">
@@ -1423,12 +1428,12 @@
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="32"/>
       <c r="C18" s="17">
@@ -1453,12 +1458,12 @@
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-    </row>
-    <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+    </row>
+    <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="34" t="s">
         <v>17</v>
@@ -1483,7 +1488,7 @@
       </c>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="32" t="s">
         <v>24</v>
@@ -1501,7 +1506,7 @@
       </c>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -1514,7 +1519,7 @@
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
     </row>
-    <row r="22" spans="1:16" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>3</v>
       </c>
@@ -1531,7 +1536,7 @@
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="32" t="str">
         <f>B16</f>
@@ -1573,7 +1578,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="32"/>
       <c r="C24" s="17">
@@ -1602,7 +1607,7 @@
       <c r="O24" s="36"/>
       <c r="P24" s="36"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" s="32"/>
       <c r="C25" s="17">
@@ -1632,7 +1637,7 @@
       <c r="O25" s="36"/>
       <c r="P25" s="36"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="32"/>
       <c r="C26" s="17">
@@ -1661,7 +1666,7 @@
       <c r="O26" s="36"/>
       <c r="P26" s="36"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="32"/>
       <c r="C27" s="17">
@@ -1691,7 +1696,7 @@
       <c r="O27" s="36"/>
       <c r="P27" s="36"/>
     </row>
-    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="34" t="s">
         <v>17</v>
@@ -1716,7 +1721,7 @@
       </c>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
       <c r="B29" s="32" t="s">
         <v>33</v>
@@ -1734,7 +1739,7 @@
       </c>
       <c r="K29" s="17"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" s="32" t="s">
         <v>34</v>
@@ -1752,7 +1757,7 @@
       </c>
       <c r="K30" s="17"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
       <c r="B31" s="32" t="s">
         <v>35</v>
@@ -1770,7 +1775,7 @@
       </c>
       <c r="K31" s="17"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
       <c r="B32" s="32" t="s">
         <v>36</v>
@@ -1788,7 +1793,7 @@
       </c>
       <c r="K32" s="17"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
       <c r="B33" s="32" t="s">
         <v>39</v>
@@ -1806,7 +1811,7 @@
       </c>
       <c r="K33" s="17"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -1819,7 +1824,7 @@
       <c r="J34" s="17"/>
       <c r="K34" s="17"/>
     </row>
-    <row r="35" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>4</v>
       </c>
@@ -1836,7 +1841,7 @@
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="16"/>
       <c r="B36" s="32" t="str">
         <f>B23</f>
@@ -1878,7 +1883,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="32"/>
       <c r="C37" s="17">
@@ -1902,12 +1907,12 @@
       <c r="I37" s="17"/>
       <c r="J37" s="17"/>
       <c r="K37" s="17"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="37"/>
-      <c r="O37" s="37"/>
-      <c r="P37" s="37"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="36"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
       <c r="B38" s="32"/>
       <c r="C38" s="17">
@@ -1931,12 +1936,12 @@
       <c r="I38" s="17"/>
       <c r="J38" s="17"/>
       <c r="K38" s="17"/>
-      <c r="M38" s="37"/>
-      <c r="N38" s="37"/>
-      <c r="O38" s="37"/>
-      <c r="P38" s="37"/>
-    </row>
-    <row r="39" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36"/>
+    </row>
+    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="34" t="s">
         <v>17</v>
@@ -1961,7 +1966,7 @@
       </c>
       <c r="K39" s="5"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
       <c r="B40" s="32" t="s">
         <v>33</v>
@@ -1979,7 +1984,7 @@
       </c>
       <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
       <c r="B41" s="32" t="s">
         <v>34</v>
@@ -1997,7 +2002,7 @@
       </c>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="16"/>
       <c r="B42" s="32" t="s">
         <v>38</v>
@@ -2015,7 +2020,7 @@
       </c>
       <c r="K42" s="17"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" s="32" t="s">
         <v>39</v>
@@ -2033,9 +2038,9 @@
       </c>
       <c r="K43" s="17"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
-      <c r="B44" s="17"/>
+      <c r="B44" s="32"/>
       <c r="C44" s="17"/>
       <c r="D44" s="17"/>
       <c r="E44" s="17"/>
@@ -2043,15 +2048,15 @@
       <c r="G44" s="17"/>
       <c r="H44" s="17"/>
       <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
+      <c r="J44" s="18"/>
       <c r="K44" s="17"/>
     </row>
-    <row r="45" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>5</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C45" s="3">
         <v>1</v>
@@ -2067,147 +2072,197 @@
         <v>20</v>
       </c>
       <c r="I45" s="6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J45" s="7">
         <f>G45*I45</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K45" s="5"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="18"/>
-      <c r="K46" s="5"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A47" s="21"/>
-      <c r="B47" s="22" t="s">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>6</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="3">
+        <v>1</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="7">
+        <f t="shared" ref="G47" si="2">PRODUCT(C47:F47)</f>
+        <v>1</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J47" s="7">
+        <f>G47*I47</f>
+        <v>1000</v>
+      </c>
+      <c r="K47" s="5"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="5"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49" s="21"/>
+      <c r="B49" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="23"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="18">
-        <f>SUM(J9:J45)</f>
-        <v>804972.08058912493</v>
-      </c>
-      <c r="K47" s="25"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="M48" s="20"/>
-      <c r="N48" s="20"/>
-      <c r="O48" s="20"/>
-      <c r="P48" s="20"/>
-      <c r="Q48" s="20"/>
-      <c r="R48" s="20"/>
-      <c r="S48" s="20"/>
-    </row>
-    <row r="49" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="26"/>
-      <c r="B49" s="27" t="s">
+      <c r="C49" s="23"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18">
+        <f>SUM(J9:J47)</f>
+        <v>796361.93058912491</v>
+      </c>
+      <c r="K49" s="25"/>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M50" s="20"/>
+      <c r="N50" s="20"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="20"/>
+      <c r="S50" s="20"/>
+    </row>
+    <row r="51" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="26"/>
+      <c r="B51" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="38">
-        <f>J47</f>
-        <v>804972.08058912493</v>
-      </c>
-      <c r="D49" s="39"/>
-      <c r="E49" s="9">
+      <c r="C51" s="43">
+        <f>J49</f>
+        <v>796361.93058912491</v>
+      </c>
+      <c r="D51" s="44"/>
+      <c r="E51" s="9">
         <v>100</v>
       </c>
-      <c r="F49" s="26"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="31"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19"/>
-      <c r="O49" s="19"/>
-      <c r="P49" s="19"/>
-      <c r="Q49" s="19"/>
-      <c r="R49" s="19"/>
-      <c r="S49" s="19"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B50" s="27" t="s">
+      <c r="F51" s="26"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="31"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="19"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="19"/>
+      <c r="Q51" s="19"/>
+      <c r="R51" s="19"/>
+      <c r="S51" s="19"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B52" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C50" s="42">
+      <c r="C52" s="47">
         <v>700000</v>
       </c>
-      <c r="D50" s="43"/>
-      <c r="E50" s="9"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B51" s="27" t="s">
+      <c r="D52" s="48"/>
+      <c r="E52" s="9"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B53" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C51" s="42">
-        <f>C50-C53-C54</f>
+      <c r="C53" s="47">
+        <f>C52-C55-C56</f>
         <v>665000</v>
       </c>
-      <c r="D51" s="43"/>
-      <c r="E51" s="9">
-        <f>C51/C49*100</f>
-        <v>82.611560827465553</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B52" s="27" t="s">
+      <c r="D53" s="48"/>
+      <c r="E53" s="9">
+        <f>C53/C51*100</f>
+        <v>83.504745073393039</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B54" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="C52" s="44">
-        <f>C49-C51</f>
-        <v>139972.08058912493</v>
-      </c>
-      <c r="D52" s="44"/>
-      <c r="E52" s="9">
-        <f>100-E51</f>
-        <v>17.388439172534447</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B53" s="27" t="s">
+      <c r="C54" s="49">
+        <f>C51-C53</f>
+        <v>131361.93058912491</v>
+      </c>
+      <c r="D54" s="49"/>
+      <c r="E54" s="9">
+        <f>100-E53</f>
+        <v>16.495254926606961</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B55" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="38">
-        <f>C50*0.03</f>
+      <c r="C55" s="43">
+        <f>C52*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D53" s="39"/>
-      <c r="E53" s="9">
+      <c r="D55" s="44"/>
+      <c r="E55" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B54" s="27" t="s">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B56" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="38">
-        <f>C50*0.02</f>
+      <c r="C56" s="43">
+        <f>C52*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D54" s="39"/>
-      <c r="E54" s="9">
+      <c r="D56" s="44"/>
+      <c r="E56" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -2215,14 +2270,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
